--- a/data/trans_camb/KIDM_A_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/KIDM_A_R-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,27 +677,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-22,62; 9,2</t>
+          <t>-21,43; 9,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,84; 10,23</t>
+          <t>-21,54; 11,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,32; 0,0</t>
+          <t>-30,54; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 15,09</t>
+          <t>-9,54; 14,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 13,56</t>
+          <t>-10,11; 14,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 9,66</t>
+          <t>-9,15; 9,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 8,88</t>
+          <t>-11,07; 7,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-17,85; -2,16</t>
+          <t>-19,63; -2,13</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-77,48; 435,4</t>
+          <t>-71,93; 374,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-84,47; 348,34</t>
+          <t>-84,84; 278,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -830,7 +830,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,17 +893,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 8,61</t>
+          <t>-2,88; 8,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 2,76</t>
+          <t>-4,44; 2,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 8,01</t>
+          <t>-4,3; 8,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,0</t>
+          <t>0,0; 5,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 4,71</t>
+          <t>-0,65; 4,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 3,23</t>
+          <t>-1,31; 3,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 4,63</t>
+          <t>-1,17; 4,67</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1119,37 +1119,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,17</t>
+          <t>0,0; 14,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,76</t>
+          <t>0,0; 13,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,87</t>
+          <t>0,0; 12,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,58</t>
+          <t>0,0; 14,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,76</t>
+          <t>0,0; 7,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,77</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,13</t>
+          <t>0,0; 10,24</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 0,0</t>
+          <t>-8,36; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 11,43</t>
+          <t>-1,65; 13,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 0,0</t>
+          <t>-7,48; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 12,4</t>
+          <t>-8,38; 12,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 8,33</t>
+          <t>-10,52; 9,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,61; -1,81</t>
+          <t>-15,59; -1,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 5,73</t>
+          <t>-5,6; 5,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 7,34</t>
+          <t>-4,84; 6,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,25; -1,02</t>
+          <t>-9,34; -1,05</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-83,57; 870,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-84,06; 604,26</t>
+          <t>-83,36; 692,79</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 20,37</t>
+          <t>-14,23; 19,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-27,0; -3,22</t>
+          <t>-24,96; -3,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-24,78; -3,16</t>
+          <t>-27,7; -3,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 13,13</t>
+          <t>-7,29; 13,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-18,49; 0,0</t>
+          <t>-14,99; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 0,0</t>
+          <t>-15,18; 0,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 13,17</t>
+          <t>-8,36; 12,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-17,01; -1,74</t>
+          <t>-15,58; -1,73</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-15,8; -1,75</t>
+          <t>-15,62; -1,74</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-79,66; 567,33</t>
+          <t>-76,55; 602,95</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1694,7 +1694,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1772,32 +1772,32 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 0,0</t>
+          <t>-12,01; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 0,0</t>
+          <t>-12,08; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 1,58</t>
+          <t>-9,69; 1,43</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 0,0</t>
+          <t>-6,47; 0,0</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 0,0</t>
+          <t>-7,65; 0,0</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 0,84</t>
+          <t>-6,23; 0,8</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 8,28</t>
+          <t>-1,33; 7,61</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 2,24</t>
+          <t>-4,22; 2,19</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 0,0</t>
+          <t>-6,68; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,15</t>
+          <t>0,0; 7,9</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,28</t>
+          <t>0,0; 6,58</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,1</t>
+          <t>0,0; 10,49</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,02; 6,1</t>
+          <t>0,02; 5,84</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 2,76</t>
+          <t>-1,29; 2,73</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 5,25</t>
+          <t>-1,29; 3,81</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 6,41</t>
+          <t>-2,19; 5,78</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 1,37</t>
+          <t>-4,81; 1,36</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 0,0</t>
+          <t>-7,0; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 5,22</t>
+          <t>-2,07; 5,02</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 0,0</t>
+          <t>-6,17; 0,0</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 5,62</t>
+          <t>-1,01; 5,88</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 4,61</t>
+          <t>-0,68; 4,62</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 0,36</t>
+          <t>-2,8; 0,5</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 2,7</t>
+          <t>-1,56; 2,56</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-79,08; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 3,4</t>
+          <t>-1,15; 3,3</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 1,09</t>
+          <t>-2,56; 1,04</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1,02</t>
+          <t>-2,67; 1,22</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 4,19</t>
+          <t>-0,22; 3,89</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 1,78</t>
+          <t>-2,01; 1,77</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,24</t>
+          <t>-2,49; 1,12</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,03; 3,07</t>
+          <t>-0,36; 2,82</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,94</t>
+          <t>-1,65; 0,77</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,49</t>
+          <t>-1,92; 0,57</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-36,98; 264,52</t>
+          <t>-42,2; 280,88</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-77,52; 113,65</t>
+          <t>-74,92; 100,41</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-90,22; 93,39</t>
+          <t>-88,86; 122,43</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 420,69</t>
+          <t>-20,01; 369,77</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-70,92; 220,32</t>
+          <t>-74,79; 189,86</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-86,42; 183,21</t>
+          <t>-86,81; 121,92</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 215,25</t>
+          <t>-14,0; 210,43</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-59,17; 83,19</t>
+          <t>-60,39; 56,47</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-75,45; 39,03</t>
+          <t>-75,98; 49,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/KIDM_A_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/KIDM_A_R-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general autopercibida regular o mala (autopercepción menor)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,27 +677,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-21,43; 9,09</t>
+          <t>-24,45; 8,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-21,54; 11,03</t>
+          <t>-20,4; 11,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,54; 0,0</t>
+          <t>-28,84; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 14,76</t>
+          <t>-10,56; 15,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 14,62</t>
+          <t>-12,53; 15,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 9,44</t>
+          <t>-10,33; 10,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 7,99</t>
+          <t>-11,47; 8,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-19,63; -2,13</t>
+          <t>-17,95; -1,96</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,81; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-71,93; 374,37</t>
+          <t>-79,1; 403,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-84,84; 278,42</t>
+          <t>-80,92; 418,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,17 +893,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 8,64</t>
+          <t>-1,5; 9,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 2,59</t>
+          <t>-4,35; 2,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 8,57</t>
+          <t>-3,39; 7,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,29</t>
+          <t>0,0; 7,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 4,64</t>
+          <t>-0,65; 4,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 3,02</t>
+          <t>-1,33; 2,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 4,67</t>
+          <t>-0,97; 4,75</t>
         </is>
       </c>
     </row>
@@ -1119,37 +1119,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,8</t>
+          <t>0,0; 14,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,16</t>
+          <t>0,0; 13,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,78</t>
+          <t>0,0; 13,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,73</t>
+          <t>0,0; 14,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,8</t>
+          <t>0,0; 7,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>0,0; 6,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,24</t>
+          <t>0,0; 10,67</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 0,0</t>
+          <t>-9,24; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 13,56</t>
+          <t>-1,66; 12,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 0,0</t>
+          <t>-8,24; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 12,28</t>
+          <t>-8,44; 12,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 9,53</t>
+          <t>-10,89; 8,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,59; -1,8</t>
+          <t>-18,71; -1,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 5,07</t>
+          <t>-5,59; 5,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 6,76</t>
+          <t>-4,77; 7,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,34; -1,05</t>
+          <t>-9,32; -0,99</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-83,57; 870,36</t>
+          <t>-87,19; 441,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-83,36; 692,79</t>
+          <t>-81,69; 668,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 19,98</t>
+          <t>-14,11; 17,67</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-24,96; -3,16</t>
+          <t>-27,29; -3,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-27,7; -3,23</t>
+          <t>-24,95; -3,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 13,21</t>
+          <t>-7,17; 13,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,99; 0,0</t>
+          <t>-17,91; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 0,0</t>
+          <t>-17,16; 0,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 12,71</t>
+          <t>-7,04; 12,96</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-15,58; -1,73</t>
+          <t>-14,19; -1,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-15,62; -1,74</t>
+          <t>-16,71; -1,77</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-76,55; 602,95</t>
+          <t>-72,01; 568,28</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1772,32 +1772,32 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 0,0</t>
+          <t>-12,97; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 0,0</t>
+          <t>-12,63; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 1,43</t>
+          <t>-11,15; 1,54</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 0,0</t>
+          <t>-6,7; 0,0</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 0,0</t>
+          <t>-7,71; 0,0</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 0,8</t>
+          <t>-5,7; 0,82</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 7,61</t>
+          <t>-2,43; 7,6</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 2,19</t>
+          <t>-4,01; 2,22</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 0,0</t>
+          <t>-7,27; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,9</t>
+          <t>0,0; 8,01</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,58</t>
+          <t>0,0; 6,35</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,49</t>
+          <t>0,0; 7,87</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,02; 5,84</t>
+          <t>-0,44; 5,62</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 2,73</t>
+          <t>-1,37; 2,26</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 3,81</t>
+          <t>-1,28; 4,36</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 5,78</t>
+          <t>-1,4; 6,04</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 1,36</t>
+          <t>-4,39; 1,37</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 0,0</t>
+          <t>-5,53; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 5,02</t>
+          <t>-1,99; 5,22</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 0,0</t>
+          <t>-4,71; 0,0</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 5,88</t>
+          <t>-1,94; 5,56</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 4,62</t>
+          <t>-0,76; 4,64</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 0,5</t>
+          <t>-3,39; 0,36</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,56</t>
+          <t>-1,62; 2,97</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,3</t>
+          <t>-1,03; 3,48</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,04</t>
+          <t>-2,4; 1,22</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 1,22</t>
+          <t>-2,77; 1,23</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 3,89</t>
+          <t>-0,22; 3,98</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,77</t>
+          <t>-1,9; 1,6</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 1,12</t>
+          <t>-2,25; 1,19</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,82</t>
+          <t>-0,08; 2,95</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,77</t>
+          <t>-1,68; 0,77</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,57</t>
+          <t>-2,02; 0,67</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-42,2; 280,88</t>
+          <t>-41,45; 287,61</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-74,92; 100,41</t>
+          <t>-74,76; 133,29</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-88,86; 122,43</t>
+          <t>-89,07; 125,78</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 369,77</t>
+          <t>-19,03; 373,53</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-74,79; 189,86</t>
+          <t>-72,48; 189,85</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-86,81; 121,92</t>
+          <t>-86,14; 146,26</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 210,43</t>
+          <t>-2,95; 227,77</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-60,39; 56,47</t>
+          <t>-60,27; 65,01</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-75,98; 49,9</t>
+          <t>-76,49; 58,66</t>
         </is>
       </c>
     </row>
